--- a/procesamiento_datos/data/EdadMediaVG.xlsx
+++ b/procesamiento_datos/data/EdadMediaVG.xlsx
@@ -386,6 +386,42 @@
       <c r="J2" s="1">
         <v>2018.0</v>
       </c>
+      <c r="K2" s="1">
+        <v>2017.0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>2016.0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>2015.0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>2014.0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>2013.0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>2012.0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>2011.0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>2010.0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>2009.0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>2008.0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2007.0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2006.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
@@ -403,6 +439,57 @@
       <c r="E3" s="1">
         <v>46.6</v>
       </c>
+      <c r="F3" s="1">
+        <v>45.9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="J3" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="L3" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="M3" s="1">
+        <v>41.3</v>
+      </c>
+      <c r="N3" s="1">
+        <v>40.7</v>
+      </c>
+      <c r="O3" s="1">
+        <v>40.3</v>
+      </c>
+      <c r="P3" s="1">
+        <v>40.1</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>40.1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>40.2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="T3" s="1">
+        <v>40.8</v>
+      </c>
+      <c r="U3" s="1">
+        <v>40.9</v>
+      </c>
+      <c r="V3" s="1">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
@@ -420,6 +507,57 @@
       <c r="E4" s="1">
         <v>47.3</v>
       </c>
+      <c r="F4" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="H4" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="J4" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="K4" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="L4" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="M4" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="N4" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="P4" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="R4" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="S4" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="T4" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="U4" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="V4" s="1">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
@@ -437,6 +575,57 @@
       <c r="E5" s="1">
         <v>45.3</v>
       </c>
+      <c r="F5" s="1">
+        <v>44.7</v>
+      </c>
+      <c r="G5" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="H5" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="I5" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="J5" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="K5" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="L5" s="1">
+        <v>32.1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="N5" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="O5" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="P5" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="S5" s="1">
+        <v>41.3</v>
+      </c>
+      <c r="T5" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="V5" s="1">
+        <v>43.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
@@ -454,6 +643,57 @@
       <c r="E6" s="1">
         <v>45.8</v>
       </c>
+      <c r="F6" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>44.6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>43.4</v>
+      </c>
+      <c r="J6" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="L6" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>41.3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>40.9</v>
+      </c>
+      <c r="O6" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="P6" s="1">
+        <v>40.3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>40.2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>40.2</v>
+      </c>
+      <c r="S6" s="1">
+        <v>40.3</v>
+      </c>
+      <c r="T6" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="U6" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="V6" s="1">
+        <v>42.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
@@ -471,6 +711,57 @@
       <c r="E7" s="1">
         <v>46.3</v>
       </c>
+      <c r="F7" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="I7" s="1">
+        <v>43.7</v>
+      </c>
+      <c r="J7" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="L7" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="N7" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="P7" s="1">
+        <v>40.3</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>40.1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>40.1</v>
+      </c>
+      <c r="T7" s="1">
+        <v>40.2</v>
+      </c>
+      <c r="U7" s="1">
+        <v>40.4</v>
+      </c>
+      <c r="V7" s="1">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
@@ -488,6 +779,57 @@
       <c r="E8" s="1">
         <v>48.7</v>
       </c>
+      <c r="F8" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>47.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="I8" s="1">
+        <v>46.2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>45.6</v>
+      </c>
+      <c r="K8" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="L8" s="1">
+        <v>44.5</v>
+      </c>
+      <c r="M8" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="O8" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="R8" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="S8" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="T8" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>40.8</v>
+      </c>
+      <c r="V8" s="1">
+        <v>39.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
@@ -505,6 +847,57 @@
       <c r="E9" s="1">
         <v>44.6</v>
       </c>
+      <c r="F9" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="H9" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="I9" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="J9" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="L9" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>39.3</v>
+      </c>
+      <c r="N9" s="1">
+        <v>38.8</v>
+      </c>
+      <c r="O9" s="1">
+        <v>38.2</v>
+      </c>
+      <c r="P9" s="1">
+        <v>37.7</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>37.2</v>
+      </c>
+      <c r="R9" s="1">
+        <v>36.8</v>
+      </c>
+      <c r="S9" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="T9" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="U9" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="V9" s="1">
+        <v>36.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
@@ -522,6 +915,57 @@
       <c r="E10" s="1">
         <v>42.6</v>
       </c>
+      <c r="F10" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>40.3</v>
+      </c>
+      <c r="I10" s="1">
+        <v>39.6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>38.8</v>
+      </c>
+      <c r="K10" s="1">
+        <v>38.1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>37.4</v>
+      </c>
+      <c r="M10" s="1">
+        <v>36.6</v>
+      </c>
+      <c r="N10" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>35.4</v>
+      </c>
+      <c r="P10" s="1">
+        <v>34.9</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="R10" s="1">
+        <v>33.9</v>
+      </c>
+      <c r="S10" s="1">
+        <v>33.2</v>
+      </c>
+      <c r="T10" s="1">
+        <v>32.9</v>
+      </c>
+      <c r="U10" s="1">
+        <v>32.6</v>
+      </c>
+      <c r="V10" s="1">
+        <v>32.6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
@@ -539,6 +983,57 @@
       <c r="E11" s="1">
         <v>44.4</v>
       </c>
+      <c r="F11" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="G11" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="K11" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="L11" s="1">
+        <v>40.8</v>
+      </c>
+      <c r="M11" s="1">
+        <v>40.2</v>
+      </c>
+      <c r="N11" s="1">
+        <v>39.7</v>
+      </c>
+      <c r="O11" s="1">
+        <v>39.2</v>
+      </c>
+      <c r="P11" s="1">
+        <v>38.9</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>38.6</v>
+      </c>
+      <c r="R11" s="1">
+        <v>38.4</v>
+      </c>
+      <c r="S11" s="1">
+        <v>38.4</v>
+      </c>
+      <c r="T11" s="1">
+        <v>38.6</v>
+      </c>
+      <c r="U11" s="1">
+        <v>39.1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>39.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
@@ -556,6 +1051,57 @@
       <c r="E12" s="1">
         <v>45.9</v>
       </c>
+      <c r="F12" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44.5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="J12" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="M12" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="N12" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="O12" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="P12" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="R12" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="S12" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="U12" s="1">
+        <v>43.7</v>
+      </c>
+      <c r="V12" s="1">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
@@ -573,6 +1119,57 @@
       <c r="E13" s="1">
         <v>47.6</v>
       </c>
+      <c r="F13" s="1">
+        <v>47.3</v>
+      </c>
+      <c r="G13" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>46.6</v>
+      </c>
+      <c r="I13" s="1">
+        <v>46.2</v>
+      </c>
+      <c r="J13" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="K13" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>44.6</v>
+      </c>
+      <c r="M13" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="O13" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="P13" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="R13" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="S13" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="T13" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="U13" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="V13" s="1">
+        <v>44.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
@@ -590,6 +1187,57 @@
       <c r="E14" s="1">
         <v>47.5</v>
       </c>
+      <c r="F14" s="1">
+        <v>47.1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="J14" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>44.5</v>
+      </c>
+      <c r="L14" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="N14" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="O14" s="1">
+        <v>42.8</v>
+      </c>
+      <c r="P14" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="R14" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="T14" s="1">
+        <v>42.8</v>
+      </c>
+      <c r="U14" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="V14" s="1">
+        <v>44.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
@@ -607,6 +1255,57 @@
       <c r="E15" s="1">
         <v>46.5</v>
       </c>
+      <c r="F15" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="H15" s="1">
+        <v>44.8</v>
+      </c>
+      <c r="I15" s="1">
+        <v>44.2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>43.7</v>
+      </c>
+      <c r="K15" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="M15" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="O15" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="P15" s="1">
+        <v>41.3</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>41.3</v>
+      </c>
+      <c r="R15" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="S15" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="T15" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="U15" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="V15" s="1">
+        <v>43.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
@@ -624,6 +1323,57 @@
       <c r="E16" s="1">
         <v>48.3</v>
       </c>
+      <c r="F16" s="1">
+        <v>47.8</v>
+      </c>
+      <c r="G16" s="1">
+        <v>47.3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>46.8</v>
+      </c>
+      <c r="I16" s="1">
+        <v>46.3</v>
+      </c>
+      <c r="J16" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="K16" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L16" s="1">
+        <v>44.7</v>
+      </c>
+      <c r="M16" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="O16" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="P16" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="R16" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="S16" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="U16" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="V16" s="1">
+        <v>43.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
@@ -641,6 +1391,57 @@
       <c r="E17" s="1">
         <v>53.1</v>
       </c>
+      <c r="F17" s="1">
+        <v>52.2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="I17" s="1">
+        <v>49.7</v>
+      </c>
+      <c r="J17" s="1">
+        <v>49.2</v>
+      </c>
+      <c r="K17" s="1">
+        <v>48.4</v>
+      </c>
+      <c r="L17" s="1">
+        <v>47.9</v>
+      </c>
+      <c r="M17" s="1">
+        <v>47.3</v>
+      </c>
+      <c r="N17" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="O17" s="1">
+        <v>46.7</v>
+      </c>
+      <c r="P17" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>46.3</v>
+      </c>
+      <c r="R17" s="1">
+        <v>46.1</v>
+      </c>
+      <c r="S17" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="T17" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="U17" s="1">
+        <v>45.6</v>
+      </c>
+      <c r="V17" s="1">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
@@ -658,6 +1459,57 @@
       <c r="E18" s="1">
         <v>46.8</v>
       </c>
+      <c r="F18" s="1">
+        <v>46.4</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45.9</v>
+      </c>
+      <c r="H18" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="I18" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="J18" s="1">
+        <v>44.3</v>
+      </c>
+      <c r="K18" s="1">
+        <v>43.8</v>
+      </c>
+      <c r="L18" s="1">
+        <v>43.4</v>
+      </c>
+      <c r="M18" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="N18" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="O18" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="R18" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="T18" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="U18" s="1">
+        <v>43.4</v>
+      </c>
+      <c r="V18" s="1">
+        <v>44.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
@@ -675,6 +1527,57 @@
       <c r="E19" s="1">
         <v>48.4</v>
       </c>
+      <c r="F19" s="1">
+        <v>47.8</v>
+      </c>
+      <c r="G19" s="1">
+        <v>47.2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>46.6</v>
+      </c>
+      <c r="I19" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="J19" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="K19" s="1">
+        <v>44.6</v>
+      </c>
+      <c r="L19" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="N19" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="P19" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="R19" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="S19" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="T19" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="U19" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="V19" s="1">
+        <v>42.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
@@ -692,6 +1595,57 @@
       <c r="E20" s="1">
         <v>51.2</v>
       </c>
+      <c r="F20" s="1">
+        <v>50.5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>50.1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>49.5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>48.8</v>
+      </c>
+      <c r="J20" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="K20" s="1">
+        <v>47.7</v>
+      </c>
+      <c r="L20" s="1">
+        <v>47.1</v>
+      </c>
+      <c r="M20" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="N20" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="O20" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="P20" s="1">
+        <v>44.5</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="S20" s="1">
+        <v>42.8</v>
+      </c>
+      <c r="T20" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="U20" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="V20" s="1">
+        <v>41.8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1">
@@ -709,6 +1663,57 @@
       <c r="E21" s="1">
         <v>36.4</v>
       </c>
+      <c r="F21" s="1">
+        <v>35.6</v>
+      </c>
+      <c r="G21" s="1">
+        <v>34.9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>34.3</v>
+      </c>
+      <c r="I21" s="1">
+        <v>33.6</v>
+      </c>
+      <c r="J21" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>32.4</v>
+      </c>
+      <c r="L21" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="M21" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="N21" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="O21" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>30.7</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="R21" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="S21" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="T21" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="U21" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="V21" s="1">
+        <v>29.8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
@@ -726,6 +1731,57 @@
       <c r="E22" s="1">
         <v>47.5</v>
       </c>
+      <c r="F22" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="H22" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="J22" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="K22" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="L22" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>43.4</v>
+      </c>
+      <c r="N22" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="P22" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="R22" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="S22" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="T22" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="U22" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
@@ -743,6 +1799,57 @@
       <c r="E23" s="1">
         <v>48.3</v>
       </c>
+      <c r="F23" s="1">
+        <v>47.8</v>
+      </c>
+      <c r="G23" s="1">
+        <v>47.2</v>
+      </c>
+      <c r="H23" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="I23" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="J23" s="1">
+        <v>45.1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>44.6</v>
+      </c>
+      <c r="L23" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>43.4</v>
+      </c>
+      <c r="N23" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="O23" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="P23" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="R23" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="T23" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="V23" s="1">
+        <v>39.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1">
@@ -760,6 +1867,57 @@
       <c r="E24" s="1">
         <v>42.0</v>
       </c>
+      <c r="F24" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>40.7</v>
+      </c>
+      <c r="H24" s="1">
+        <v>40.1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>39.3</v>
+      </c>
+      <c r="J24" s="1">
+        <v>38.6</v>
+      </c>
+      <c r="K24" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>37.3</v>
+      </c>
+      <c r="M24" s="1">
+        <v>36.6</v>
+      </c>
+      <c r="N24" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="P24" s="1">
+        <v>34.9</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="R24" s="1">
+        <v>33.9</v>
+      </c>
+      <c r="S24" s="1">
+        <v>33.5</v>
+      </c>
+      <c r="T24" s="1">
+        <v>33.2</v>
+      </c>
+      <c r="U24" s="1">
+        <v>32.9</v>
+      </c>
+      <c r="V24" s="1">
+        <v>32.6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1">
@@ -777,6 +1935,57 @@
       <c r="E25" s="1">
         <v>47.4</v>
       </c>
+      <c r="F25" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="G25" s="1">
+        <v>46.3</v>
+      </c>
+      <c r="H25" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="I25" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="J25" s="1">
+        <v>44.6</v>
+      </c>
+      <c r="K25" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="M25" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="N25" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="O25" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="R25" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="S25" s="1">
+        <v>40.9</v>
+      </c>
+      <c r="T25" s="1">
+        <v>40.8</v>
+      </c>
+      <c r="U25" s="1">
+        <v>40.7</v>
+      </c>
+      <c r="V25" s="1">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1">
@@ -794,6 +2003,57 @@
       <c r="E26" s="1">
         <v>48.4</v>
       </c>
+      <c r="F26" s="1">
+        <v>47.8</v>
+      </c>
+      <c r="G26" s="1">
+        <v>47.3</v>
+      </c>
+      <c r="H26" s="1">
+        <v>46.8</v>
+      </c>
+      <c r="I26" s="1">
+        <v>46.2</v>
+      </c>
+      <c r="J26" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="K26" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="L26" s="1">
+        <v>44.8</v>
+      </c>
+      <c r="M26" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="N26" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="O26" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="R26" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="S26" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="T26" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="U26" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="V26" s="1">
+        <v>41.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1">
@@ -811,6 +2071,57 @@
       <c r="E27" s="1">
         <v>49.5</v>
       </c>
+      <c r="F27" s="1">
+        <v>48.9</v>
+      </c>
+      <c r="G27" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="H27" s="1">
+        <v>47.6</v>
+      </c>
+      <c r="I27" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="K27" s="1">
+        <v>45.9</v>
+      </c>
+      <c r="L27" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="M27" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="N27" s="1">
+        <v>44.5</v>
+      </c>
+      <c r="O27" s="1">
+        <v>44.3</v>
+      </c>
+      <c r="P27" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="R27" s="1">
+        <v>43.7</v>
+      </c>
+      <c r="S27" s="1">
+        <v>43.8</v>
+      </c>
+      <c r="T27" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="U27" s="1">
+        <v>44.3</v>
+      </c>
+      <c r="V27" s="1">
+        <v>44.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1">
@@ -828,6 +2139,57 @@
       <c r="E28" s="1">
         <v>35.7</v>
       </c>
+      <c r="F28" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>34.2</v>
+      </c>
+      <c r="H28" s="1">
+        <v>33.6</v>
+      </c>
+      <c r="I28" s="1">
+        <v>32.9</v>
+      </c>
+      <c r="J28" s="1">
+        <v>32.3</v>
+      </c>
+      <c r="K28" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="L28" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="M28" s="1">
+        <v>31.1</v>
+      </c>
+      <c r="N28" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="O28" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="P28" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="R28" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="S28" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="T28" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="U28" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="V28" s="1">
+        <v>29.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1">
@@ -845,6 +2207,57 @@
       <c r="E29" s="1">
         <v>46.3</v>
       </c>
+      <c r="F29" s="1">
+        <v>45.9</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="H29" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="I29" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="J29" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="K29" s="1">
+        <v>43.4</v>
+      </c>
+      <c r="L29" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="M29" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="N29" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="O29" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="P29" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="R29" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="S29" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="T29" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="U29" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="V29" s="1">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1">
@@ -862,6 +2275,57 @@
       <c r="E30" s="1">
         <v>51.8</v>
       </c>
+      <c r="F30" s="1">
+        <v>51.3</v>
+      </c>
+      <c r="G30" s="1">
+        <v>50.7</v>
+      </c>
+      <c r="H30" s="1">
+        <v>49.7</v>
+      </c>
+      <c r="I30" s="1">
+        <v>48.7</v>
+      </c>
+      <c r="J30" s="1">
+        <v>47.8</v>
+      </c>
+      <c r="K30" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="L30" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>45.4</v>
+      </c>
+      <c r="N30" s="1">
+        <v>44.8</v>
+      </c>
+      <c r="O30" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="P30" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="S30" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="T30" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="U30" s="1">
+        <v>40.8</v>
+      </c>
+      <c r="V30" s="1">
+        <v>41.0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1">
@@ -879,6 +2343,57 @@
       <c r="E31" s="1">
         <v>48.7</v>
       </c>
+      <c r="F31" s="1">
+        <v>47.9</v>
+      </c>
+      <c r="G31" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>46.3</v>
+      </c>
+      <c r="I31" s="1">
+        <v>45.6</v>
+      </c>
+      <c r="J31" s="1">
+        <v>44.8</v>
+      </c>
+      <c r="K31" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="N31" s="1">
+        <v>40.9</v>
+      </c>
+      <c r="O31" s="1">
+        <v>40.1</v>
+      </c>
+      <c r="P31" s="1">
+        <v>39.8</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>39.2</v>
+      </c>
+      <c r="R31" s="1">
+        <v>38.7</v>
+      </c>
+      <c r="S31" s="1">
+        <v>38.4</v>
+      </c>
+      <c r="T31" s="1">
+        <v>38.2</v>
+      </c>
+      <c r="U31" s="1">
+        <v>38.5</v>
+      </c>
+      <c r="V31" s="1">
+        <v>39.3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1">
@@ -896,8 +2411,62 @@
       <c r="E32" s="1">
         <v>49.5</v>
       </c>
+      <c r="F32" s="1">
+        <v>48.9</v>
+      </c>
+      <c r="G32" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="H32" s="1">
+        <v>47.2</v>
+      </c>
+      <c r="I32" s="1">
+        <v>46.4</v>
+      </c>
+      <c r="J32" s="1">
+        <v>45.6</v>
+      </c>
+      <c r="K32" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="L32" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="M32" s="1">
+        <v>43.6</v>
+      </c>
+      <c r="N32" s="1">
+        <v>43.1</v>
+      </c>
+      <c r="O32" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="P32" s="1">
+        <v>42.7</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="R32" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="S32" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="T32" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="U32" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="V32" s="1">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="33">
+      <c r="A33" s="1">
+        <v>31.0</v>
+      </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
@@ -909,6 +2478,57 @@
       </c>
       <c r="E33" s="1">
         <v>33.4</v>
+      </c>
+      <c r="F33" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>32.6</v>
+      </c>
+      <c r="H33" s="1">
+        <v>32.4</v>
+      </c>
+      <c r="I33" s="1">
+        <v>32.2</v>
+      </c>
+      <c r="J33" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>31.6</v>
+      </c>
+      <c r="L33" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="M33" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="N33" s="1">
+        <v>32.3</v>
+      </c>
+      <c r="O33" s="1">
+        <v>32.5</v>
+      </c>
+      <c r="P33" s="1">
+        <v>31.3</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>64.4</v>
+      </c>
+      <c r="R33" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>63.2</v>
+      </c>
+      <c r="T33" s="1">
+        <v>62.2</v>
+      </c>
+      <c r="U33" s="1">
+        <v>63.8</v>
+      </c>
+      <c r="V33" s="1">
+        <v>62.8</v>
       </c>
     </row>
   </sheetData>
